--- a/CT.xlsx
+++ b/CT.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -364,17 +364,17 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Cidade</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Ano</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Mês</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Cidade</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -396,17 +396,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Blumenau</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Janeiro</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
         </is>
       </c>
       <c r="F2" s="2">
@@ -416,17 +416,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Blumenau</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Fevereiro</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
         </is>
       </c>
       <c r="F3" s="2">
@@ -436,17 +436,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Blumenau</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Março</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
         </is>
       </c>
       <c r="D4">
@@ -459,24 +459,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Blumenau</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Abril</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
-        </is>
-      </c>
       <c r="D5">
-        <v>548.29</v>
+        <v>530.74</v>
       </c>
       <c r="E5">
-        <v>2.58</v>
+        <v>-0.7</v>
       </c>
       <c r="F5" s="2">
         <v>45017</v>
@@ -485,17 +485,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Blumenau</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Maio</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
         </is>
       </c>
       <c r="F6" s="2">
@@ -505,21 +505,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Blumenau</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Junho</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
-        </is>
-      </c>
       <c r="D7">
-        <v>567.5700000000001</v>
+        <v>560.29</v>
       </c>
       <c r="F7" s="2">
         <v>45078</v>
@@ -528,24 +528,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Blumenau</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Julho</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
-        </is>
-      </c>
       <c r="D8">
-        <v>532.71</v>
+        <v>547.9400000000001</v>
       </c>
       <c r="E8">
-        <v>-6.14</v>
+        <v>-2.2</v>
       </c>
       <c r="F8" s="2">
         <v>45108</v>
@@ -554,24 +554,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Blumenau</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Agosto</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
-        </is>
-      </c>
       <c r="D9">
-        <v>537.4</v>
+        <v>528.54</v>
       </c>
       <c r="E9">
-        <v>0.88</v>
+        <v>-3.54</v>
       </c>
       <c r="F9" s="2">
         <v>45139</v>
@@ -580,24 +580,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Blumenau</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Setembro</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
-        </is>
-      </c>
       <c r="D10">
-        <v>547.47</v>
+        <v>514.08</v>
       </c>
       <c r="E10">
-        <v>1.87</v>
+        <v>-2.74</v>
       </c>
       <c r="F10" s="2">
         <v>45170</v>
@@ -606,24 +606,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Blumenau</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Outubro</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
-        </is>
-      </c>
       <c r="D11">
-        <v>505.62</v>
+        <v>504.5</v>
       </c>
       <c r="E11">
-        <v>-7.64</v>
+        <v>-1.86</v>
       </c>
       <c r="F11" s="2">
         <v>45200</v>
@@ -632,24 +632,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Blumenau</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Novembro</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
-        </is>
-      </c>
       <c r="D12">
-        <v>510.87</v>
+        <v>547.5700000000001</v>
       </c>
       <c r="E12">
-        <v>1.04</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="F12" s="2">
         <v>45231</v>
@@ -658,24 +658,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Blumenau</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Dezembro</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
-        </is>
-      </c>
       <c r="D13">
-        <v>518.92</v>
+        <v>542.55</v>
       </c>
       <c r="E13">
-        <v>1.58</v>
+        <v>-0.92</v>
       </c>
       <c r="F13" s="2">
         <v>45261</v>
@@ -684,24 +684,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Janeiro</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
-        </is>
-      </c>
       <c r="D14">
-        <v>539.15</v>
+        <v>520.3200000000001</v>
       </c>
       <c r="E14">
-        <v>3.9</v>
+        <v>-4.1</v>
       </c>
       <c r="F14" s="2">
         <v>45292</v>
@@ -710,24 +710,18 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>Fevereiro</t>
         </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>540.36</v>
-      </c>
-      <c r="E15">
-        <v>0.23</v>
       </c>
       <c r="F15" s="2">
         <v>45323</v>
@@ -736,25 +730,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Março</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
         </is>
       </c>
       <c r="D16">
         <v>514.03</v>
       </c>
-      <c r="E16">
-        <v>-4.87</v>
-      </c>
       <c r="F16" s="2">
         <v>45352</v>
       </c>
@@ -762,17 +753,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>Abril</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
         </is>
       </c>
       <c r="F17" s="2">
@@ -782,17 +773,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Maio</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
         </is>
       </c>
       <c r="D18">
@@ -805,24 +796,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>Junho</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
-        </is>
-      </c>
       <c r="D19">
-        <v>628.8099999999999</v>
+        <v>610.36</v>
       </c>
       <c r="E19">
-        <v>4.34</v>
+        <v>1.27</v>
       </c>
       <c r="F19" s="2">
         <v>45444</v>
@@ -831,24 +822,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Julho</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
-        </is>
-      </c>
       <c r="D20">
-        <v>610.4400000000001</v>
+        <v>563.7</v>
       </c>
       <c r="E20">
-        <v>-2.92</v>
+        <v>-7.64</v>
       </c>
       <c r="F20" s="2">
         <v>45474</v>
@@ -857,24 +848,24 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>Agosto</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
         </is>
       </c>
       <c r="D21">
         <v>538.58</v>
       </c>
       <c r="E21">
-        <v>-11.77</v>
+        <v>-4.46</v>
       </c>
       <c r="F21" s="2">
         <v>45505</v>
@@ -883,24 +874,24 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Setembro</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
-        </is>
-      </c>
       <c r="D22">
-        <v>547.16</v>
+        <v>553.73</v>
       </c>
       <c r="E22">
-        <v>1.59</v>
+        <v>2.81</v>
       </c>
       <c r="F22" s="2">
         <v>45536</v>
@@ -909,24 +900,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>Outubro</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
-        </is>
-      </c>
       <c r="D23">
-        <v>553.84</v>
+        <v>558.39</v>
       </c>
       <c r="E23">
-        <v>1.22</v>
+        <v>0.84</v>
       </c>
       <c r="F23" s="2">
         <v>45566</v>
@@ -935,24 +926,24 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>Novembro</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
-        </is>
-      </c>
       <c r="D24">
-        <v>578.97</v>
+        <v>572.6900000000001</v>
       </c>
       <c r="E24">
-        <v>4.54</v>
+        <v>2.56</v>
       </c>
       <c r="F24" s="2">
         <v>45597</v>
@@ -961,24 +952,24 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>Dezembro</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
-        </is>
-      </c>
       <c r="D25">
-        <v>587.13</v>
+        <v>581.91</v>
       </c>
       <c r="E25">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="F25" s="2">
         <v>45627</v>
@@ -987,24 +978,24 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Blumenau</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Janeiro</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
-        </is>
-      </c>
       <c r="D26">
-        <v>585.16</v>
+        <v>599.3099999999999</v>
       </c>
       <c r="E26">
-        <v>-0.34</v>
+        <v>2.99</v>
       </c>
       <c r="F26" s="2">
         <v>45658</v>
@@ -1013,330 +1004,474 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Gaspar</t>
-        </is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>645.51</v>
+      </c>
+      <c r="E27">
+        <v>7.71</v>
       </c>
       <c r="F27" s="2">
-        <v>45292</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D28">
-        <v>596.15</v>
+        <v>665.86</v>
+      </c>
+      <c r="E28">
+        <v>3.15</v>
       </c>
       <c r="F28" s="2">
-        <v>45323</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gaspar</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>635.98</v>
-      </c>
-      <c r="E29">
-        <v>6.68</v>
+          <t>Abril</t>
+        </is>
       </c>
       <c r="F29" s="2">
-        <v>45352</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Gaspar</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>619.71</v>
-      </c>
-      <c r="E30">
-        <v>-2.56</v>
+          <t>Janeiro</t>
+        </is>
       </c>
       <c r="F30" s="2">
-        <v>45383</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="D31">
-        <v>610.02</v>
-      </c>
-      <c r="E31">
-        <v>-1.56</v>
+        <v>596.15</v>
       </c>
       <c r="F31" s="2">
-        <v>45413</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D32">
-        <v>629.77</v>
+        <v>635.98</v>
       </c>
       <c r="E32">
-        <v>3.24</v>
+        <v>6.68</v>
       </c>
       <c r="F32" s="2">
-        <v>45444</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D33">
-        <v>581.67</v>
+        <v>619.71</v>
       </c>
       <c r="E33">
-        <v>-7.64</v>
+        <v>-2.56</v>
       </c>
       <c r="F33" s="2">
-        <v>45474</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D34">
-        <v>580.99</v>
+        <v>610.02</v>
       </c>
       <c r="E34">
-        <v>-0.12</v>
+        <v>-1.56</v>
       </c>
       <c r="F34" s="2">
-        <v>45505</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D35">
-        <v>588.79</v>
+        <v>629.77</v>
       </c>
       <c r="E35">
-        <v>1.34</v>
+        <v>3.24</v>
       </c>
       <c r="F35" s="2">
-        <v>45536</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D36">
-        <v>554.67</v>
+        <v>581.67</v>
       </c>
       <c r="E36">
-        <v>-5.8</v>
+        <v>-7.64</v>
       </c>
       <c r="F36" s="2">
-        <v>45566</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D37">
-        <v>591.6</v>
+        <v>580.99</v>
       </c>
       <c r="E37">
-        <v>6.66</v>
+        <v>-0.12</v>
       </c>
       <c r="F37" s="2">
-        <v>45597</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D38">
-        <v>565.35</v>
+        <v>588.79</v>
       </c>
       <c r="E38">
-        <v>-4.44</v>
+        <v>1.34</v>
       </c>
       <c r="F38" s="2">
-        <v>45627</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>554.67</v>
+      </c>
+      <c r="E39">
+        <v>-5.8</v>
+      </c>
+      <c r="F39" s="2">
+        <v>45566</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
+      <c r="D40">
+        <v>591.6</v>
+      </c>
+      <c r="E40">
+        <v>6.66</v>
+      </c>
+      <c r="F40" s="2">
+        <v>45597</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dezembro</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>565.35</v>
+      </c>
+      <c r="E41">
+        <v>-4.44</v>
+      </c>
+      <c r="F41" s="2">
+        <v>45627</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Janeiro</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Gaspar</t>
-        </is>
-      </c>
-      <c r="D39">
+      <c r="D42">
         <v>585.25</v>
       </c>
-      <c r="E39">
+      <c r="E42">
         <v>3.52</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F42" s="2">
         <v>45658</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>610.33</v>
+      </c>
+      <c r="E43">
+        <v>4.28</v>
+      </c>
+      <c r="F43" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>615.97</v>
+      </c>
+      <c r="E44">
+        <v>0.92</v>
+      </c>
+      <c r="F44" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="F45" s="2">
+        <v>45748</v>
       </c>
     </row>
   </sheetData>

--- a/CT.xlsx
+++ b/CT.xlsx
@@ -1069,6 +1069,12 @@
           <t>Abril</t>
         </is>
       </c>
+      <c r="D29">
+        <v>680.66</v>
+      </c>
+      <c r="E29">
+        <v>2.22</v>
+      </c>
       <c r="F29" s="2">
         <v>45748</v>
       </c>

--- a/CT.xlsx
+++ b/CT.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -1082,96 +1082,81 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="F30" s="2">
-        <v>45292</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>596.15</v>
+          <t>Junho</t>
+        </is>
       </c>
       <c r="F31" s="2">
-        <v>45323</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Março</t>
-        </is>
-      </c>
-      <c r="D32">
-        <v>635.98</v>
-      </c>
-      <c r="E32">
-        <v>6.68</v>
+          <t>Julho</t>
+        </is>
       </c>
       <c r="F32" s="2">
-        <v>45352</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Abril</t>
-        </is>
-      </c>
-      <c r="D33">
-        <v>619.71</v>
-      </c>
-      <c r="E33">
-        <v>-2.56</v>
+          <t>Agosto</t>
+        </is>
       </c>
       <c r="F33" s="2">
-        <v>45383</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="34">
@@ -1187,17 +1172,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Maio</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>610.02</v>
-      </c>
-      <c r="E34">
-        <v>-1.56</v>
+          <t>Janeiro</t>
+        </is>
       </c>
       <c r="F34" s="2">
-        <v>45413</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="35">
@@ -1213,17 +1192,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="D35">
-        <v>629.77</v>
-      </c>
-      <c r="E35">
-        <v>3.24</v>
+        <v>596.15</v>
       </c>
       <c r="F35" s="2">
-        <v>45444</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="36">
@@ -1239,17 +1215,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D36">
-        <v>581.67</v>
+        <v>635.98</v>
       </c>
       <c r="E36">
-        <v>-7.64</v>
+        <v>6.68</v>
       </c>
       <c r="F36" s="2">
-        <v>45474</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="37">
@@ -1265,17 +1241,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D37">
-        <v>580.99</v>
+        <v>619.71</v>
       </c>
       <c r="E37">
-        <v>-0.12</v>
+        <v>-2.56</v>
       </c>
       <c r="F37" s="2">
-        <v>45505</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="38">
@@ -1291,17 +1267,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D38">
-        <v>588.79</v>
+        <v>610.02</v>
       </c>
       <c r="E38">
-        <v>1.34</v>
+        <v>-1.56</v>
       </c>
       <c r="F38" s="2">
-        <v>45536</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="39">
@@ -1317,17 +1293,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D39">
-        <v>554.67</v>
+        <v>629.77</v>
       </c>
       <c r="E39">
-        <v>-5.8</v>
+        <v>3.24</v>
       </c>
       <c r="F39" s="2">
-        <v>45566</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="40">
@@ -1343,17 +1319,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D40">
-        <v>591.6</v>
+        <v>581.67</v>
       </c>
       <c r="E40">
-        <v>6.66</v>
+        <v>-7.64</v>
       </c>
       <c r="F40" s="2">
-        <v>45597</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="41">
@@ -1369,17 +1345,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D41">
-        <v>565.35</v>
+        <v>580.99</v>
       </c>
       <c r="E41">
-        <v>-4.44</v>
+        <v>-0.12</v>
       </c>
       <c r="F41" s="2">
-        <v>45627</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="42">
@@ -1390,22 +1366,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D42">
-        <v>585.25</v>
+        <v>588.79</v>
       </c>
       <c r="E42">
-        <v>3.52</v>
+        <v>1.34</v>
       </c>
       <c r="F42" s="2">
-        <v>45658</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="43">
@@ -1416,22 +1392,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D43">
-        <v>610.33</v>
+        <v>554.67</v>
       </c>
       <c r="E43">
-        <v>4.28</v>
+        <v>-5.8</v>
       </c>
       <c r="F43" s="2">
-        <v>45689</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="44">
@@ -1442,22 +1418,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D44">
-        <v>615.97</v>
+        <v>591.6</v>
       </c>
       <c r="E44">
-        <v>0.92</v>
+        <v>6.66</v>
       </c>
       <c r="F44" s="2">
-        <v>45717</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="45">
@@ -1468,16 +1444,200 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Dezembro</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>565.35</v>
+      </c>
+      <c r="E45">
+        <v>-4.44</v>
+      </c>
+      <c r="F45" s="2">
+        <v>45627</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>585.25</v>
+      </c>
+      <c r="E46">
+        <v>3.52</v>
+      </c>
+      <c r="F46" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="D47">
+        <v>610.33</v>
+      </c>
+      <c r="E47">
+        <v>4.28</v>
+      </c>
+      <c r="F47" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>615.97</v>
+      </c>
+      <c r="E48">
+        <v>0.92</v>
+      </c>
+      <c r="F48" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>Abril</t>
         </is>
       </c>
-      <c r="F45" s="2">
+      <c r="F49" s="2">
         <v>45748</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="F50" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="F51" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="F52" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="F53" s="2">
+        <v>45870</v>
       </c>
     </row>
   </sheetData>

--- a/CT.xlsx
+++ b/CT.xlsx
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>504.5</v>
+        <v>806.37</v>
       </c>
       <c r="E11">
-        <v>-1.86</v>
+        <v>56.86</v>
       </c>
       <c r="F11" s="2">
         <v>45200</v>
@@ -649,7 +649,7 @@
         <v>547.5700000000001</v>
       </c>
       <c r="E12">
-        <v>8.539999999999999</v>
+        <v>-32.09</v>
       </c>
       <c r="F12" s="2">
         <v>45231</v>
@@ -723,6 +723,12 @@
           <t>Fevereiro</t>
         </is>
       </c>
+      <c r="D15">
+        <v>548.96</v>
+      </c>
+      <c r="E15">
+        <v>5.5</v>
+      </c>
       <c r="F15" s="2">
         <v>45323</v>
       </c>
@@ -746,6 +752,9 @@
       <c r="D16">
         <v>514.03</v>
       </c>
+      <c r="E16">
+        <v>-6.36</v>
+      </c>
       <c r="F16" s="2">
         <v>45352</v>
       </c>
@@ -940,10 +949,10 @@
         </is>
       </c>
       <c r="D24">
-        <v>572.6900000000001</v>
+        <v>585.47</v>
       </c>
       <c r="E24">
-        <v>2.56</v>
+        <v>4.85</v>
       </c>
       <c r="F24" s="2">
         <v>45597</v>
@@ -966,10 +975,10 @@
         </is>
       </c>
       <c r="D25">
-        <v>581.91</v>
+        <v>596.52</v>
       </c>
       <c r="E25">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="F25" s="2">
         <v>45627</v>
@@ -995,7 +1004,7 @@
         <v>599.3099999999999</v>
       </c>
       <c r="E26">
-        <v>2.99</v>
+        <v>0.47</v>
       </c>
       <c r="F26" s="2">
         <v>45658</v>
@@ -1095,6 +1104,12 @@
           <t>Maio</t>
         </is>
       </c>
+      <c r="D30">
+        <v>652.15</v>
+      </c>
+      <c r="E30">
+        <v>-4.19</v>
+      </c>
       <c r="F30" s="2">
         <v>45778</v>
       </c>
@@ -1115,6 +1130,12 @@
           <t>Junho</t>
         </is>
       </c>
+      <c r="D31">
+        <v>682.8</v>
+      </c>
+      <c r="E31">
+        <v>4.7</v>
+      </c>
       <c r="F31" s="2">
         <v>45809</v>
       </c>
@@ -1135,6 +1156,12 @@
           <t>Julho</t>
         </is>
       </c>
+      <c r="D32">
+        <v>680.6</v>
+      </c>
+      <c r="E32">
+        <v>-0.32</v>
+      </c>
       <c r="F32" s="2">
         <v>45839</v>
       </c>
@@ -1154,6 +1181,12 @@
         <is>
           <t>Agosto</t>
         </is>
+      </c>
+      <c r="D33">
+        <v>669.9400000000001</v>
+      </c>
+      <c r="E33">
+        <v>-1.57</v>
       </c>
       <c r="F33" s="2">
         <v>45870</v>

--- a/CT.xlsx
+++ b/CT.xlsx
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>530.74</v>
+        <v>531.49</v>
       </c>
       <c r="E5">
-        <v>-0.7</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F5" s="2">
         <v>45017</v>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>547.9400000000001</v>
+        <v>532.25</v>
       </c>
       <c r="E8">
-        <v>-2.2</v>
+        <v>-5</v>
       </c>
       <c r="F8" s="2">
         <v>45108</v>
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>528.54</v>
+        <v>523.8</v>
       </c>
       <c r="E9">
-        <v>-3.54</v>
+        <v>-1.59</v>
       </c>
       <c r="F9" s="2">
         <v>45139</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>514.08</v>
+        <v>516.0599999999999</v>
       </c>
       <c r="E10">
-        <v>-2.74</v>
+        <v>-1.48</v>
       </c>
       <c r="F10" s="2">
         <v>45170</v>
@@ -619,12 +619,6 @@
           <t>Outubro</t>
         </is>
       </c>
-      <c r="D11">
-        <v>806.37</v>
-      </c>
-      <c r="E11">
-        <v>56.86</v>
-      </c>
       <c r="F11" s="2">
         <v>45200</v>
       </c>
@@ -648,9 +642,6 @@
       <c r="D12">
         <v>547.5700000000001</v>
       </c>
-      <c r="E12">
-        <v>-32.09</v>
-      </c>
       <c r="F12" s="2">
         <v>45231</v>
       </c>
@@ -672,10 +663,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>542.55</v>
+        <v>515.79</v>
       </c>
       <c r="E13">
-        <v>-0.92</v>
+        <v>-5.8</v>
       </c>
       <c r="F13" s="2">
         <v>45261</v>
@@ -701,7 +692,7 @@
         <v>520.3200000000001</v>
       </c>
       <c r="E14">
-        <v>-4.1</v>
+        <v>0.88</v>
       </c>
       <c r="F14" s="2">
         <v>45292</v>

--- a/CT.xlsx
+++ b/CT.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -1186,44 +1186,45 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Janeiro</t>
-        </is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>712.47</v>
+      </c>
+      <c r="E34">
+        <v>6.35</v>
       </c>
       <c r="F34" s="2">
-        <v>45292</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Fevereiro</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D35">
-        <v>596.15</v>
-      </c>
-      <c r="F35" s="2">
-        <v>45323</v>
+        <v>619.4400000000001</v>
+      </c>
+      <c r="E35">
+        <v>-13.06</v>
       </c>
     </row>
     <row r="36">
@@ -1239,17 +1240,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Março</t>
-        </is>
-      </c>
-      <c r="D36">
-        <v>635.98</v>
-      </c>
-      <c r="E36">
-        <v>6.68</v>
+          <t>Janeiro</t>
+        </is>
       </c>
       <c r="F36" s="2">
-        <v>45352</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="37">
@@ -1265,17 +1260,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="D37">
-        <v>619.71</v>
-      </c>
-      <c r="E37">
-        <v>-2.56</v>
+        <v>596.15</v>
       </c>
       <c r="F37" s="2">
-        <v>45383</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="38">
@@ -1291,17 +1283,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D38">
-        <v>610.02</v>
+        <v>635.98</v>
       </c>
       <c r="E38">
-        <v>-1.56</v>
+        <v>6.68</v>
       </c>
       <c r="F38" s="2">
-        <v>45413</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="39">
@@ -1317,17 +1309,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D39">
-        <v>629.77</v>
+        <v>619.71</v>
       </c>
       <c r="E39">
-        <v>3.24</v>
+        <v>-2.56</v>
       </c>
       <c r="F39" s="2">
-        <v>45444</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="40">
@@ -1343,17 +1335,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D40">
-        <v>581.67</v>
+        <v>610.02</v>
       </c>
       <c r="E40">
-        <v>-7.64</v>
+        <v>-1.56</v>
       </c>
       <c r="F40" s="2">
-        <v>45474</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="41">
@@ -1369,17 +1361,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D41">
-        <v>580.99</v>
+        <v>629.77</v>
       </c>
       <c r="E41">
-        <v>-0.12</v>
+        <v>3.24</v>
       </c>
       <c r="F41" s="2">
-        <v>45505</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="42">
@@ -1395,17 +1387,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D42">
-        <v>588.79</v>
+        <v>581.67</v>
       </c>
       <c r="E42">
-        <v>1.34</v>
+        <v>-7.64</v>
       </c>
       <c r="F42" s="2">
-        <v>45536</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="43">
@@ -1421,17 +1413,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D43">
-        <v>554.67</v>
+        <v>580.99</v>
       </c>
       <c r="E43">
-        <v>-5.8</v>
+        <v>-0.12</v>
       </c>
       <c r="F43" s="2">
-        <v>45566</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="44">
@@ -1447,17 +1439,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D44">
-        <v>591.6</v>
+        <v>588.79</v>
       </c>
       <c r="E44">
-        <v>6.66</v>
+        <v>1.34</v>
       </c>
       <c r="F44" s="2">
-        <v>45597</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="45">
@@ -1473,17 +1465,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D45">
-        <v>565.35</v>
+        <v>554.67</v>
       </c>
       <c r="E45">
-        <v>-4.44</v>
+        <v>-5.8</v>
       </c>
       <c r="F45" s="2">
-        <v>45627</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="46">
@@ -1494,22 +1486,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D46">
-        <v>585.25</v>
+        <v>591.6</v>
       </c>
       <c r="E46">
-        <v>3.52</v>
+        <v>6.66</v>
       </c>
       <c r="F46" s="2">
-        <v>45658</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="47">
@@ -1520,22 +1512,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="D47">
-        <v>610.33</v>
+        <v>565.35</v>
       </c>
       <c r="E47">
-        <v>4.28</v>
+        <v>-4.44</v>
       </c>
       <c r="F47" s="2">
-        <v>45689</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="48">
@@ -1551,17 +1543,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="D48">
-        <v>615.97</v>
+        <v>585.25</v>
       </c>
       <c r="E48">
-        <v>0.92</v>
+        <v>3.52</v>
       </c>
       <c r="F48" s="2">
-        <v>45717</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="49">
@@ -1577,11 +1569,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Abril</t>
-        </is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="D49">
+        <v>610.33</v>
+      </c>
+      <c r="E49">
+        <v>4.28</v>
       </c>
       <c r="F49" s="2">
-        <v>45748</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="50">
@@ -1597,11 +1595,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Maio</t>
-        </is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="D50">
+        <v>615.97</v>
+      </c>
+      <c r="E50">
+        <v>0.92</v>
       </c>
       <c r="F50" s="2">
-        <v>45778</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="51">
@@ -1617,11 +1621,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="F51" s="2">
-        <v>45809</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="52">
@@ -1637,11 +1641,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="F52" s="2">
-        <v>45839</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="53">
@@ -1657,11 +1661,71 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="F53" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="F54" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>Agosto</t>
         </is>
       </c>
-      <c r="F53" s="2">
+      <c r="F55" s="2">
         <v>45870</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="F56" s="2">
+        <v>45901</v>
       </c>
     </row>
   </sheetData>

--- a/CT.xlsx
+++ b/CT.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="D34">
-        <v>712.47</v>
+        <v>659.99</v>
       </c>
       <c r="E34">
-        <v>6.35</v>
+        <v>-1.49</v>
       </c>
       <c r="F34" s="2">
         <v>45901</v>
@@ -1220,11 +1220,19 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
       <c r="D35">
-        <v>619.4400000000001</v>
+        <v>610.76</v>
       </c>
       <c r="E35">
-        <v>-13.06</v>
+        <v>-7.46</v>
+      </c>
+      <c r="F35" s="2">
+        <v>45931</v>
       </c>
     </row>
     <row r="36">
@@ -1726,6 +1734,26 @@
       </c>
       <c r="F56" s="2">
         <v>45901</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="F57" s="2">
+        <v>45931</v>
       </c>
     </row>
   </sheetData>

--- a/CT.xlsx
+++ b/CT.xlsx
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="D35">
-        <v>610.76</v>
+        <v>642.1900000000001</v>
       </c>
       <c r="E35">
-        <v>-7.46</v>
+        <v>-2.7</v>
       </c>
       <c r="F35" s="2">
         <v>45931</v>

--- a/CT.xlsx
+++ b/CT.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -1238,21 +1238,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Janeiro</t>
-        </is>
+          <t>Novembro</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>637.71</v>
+      </c>
+      <c r="E36">
+        <v>-0.7</v>
       </c>
       <c r="F36" s="2">
-        <v>45292</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="37">
@@ -1268,14 +1274,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
-        </is>
-      </c>
-      <c r="D37">
-        <v>596.15</v>
+          <t>Janeiro</t>
+        </is>
       </c>
       <c r="F37" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="38">
@@ -1291,17 +1294,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="D38">
-        <v>635.98</v>
-      </c>
-      <c r="E38">
-        <v>6.68</v>
+        <v>596.15</v>
       </c>
       <c r="F38" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="39">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D39">
-        <v>619.71</v>
+        <v>635.98</v>
       </c>
       <c r="E39">
-        <v>-2.56</v>
+        <v>6.68</v>
       </c>
       <c r="F39" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="40">
@@ -1343,17 +1343,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D40">
-        <v>610.02</v>
+        <v>619.71</v>
       </c>
       <c r="E40">
-        <v>-1.56</v>
+        <v>-2.56</v>
       </c>
       <c r="F40" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="41">
@@ -1369,17 +1369,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D41">
-        <v>629.77</v>
+        <v>610.02</v>
       </c>
       <c r="E41">
-        <v>3.24</v>
+        <v>-1.56</v>
       </c>
       <c r="F41" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="42">
@@ -1395,17 +1395,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D42">
-        <v>581.67</v>
+        <v>629.77</v>
       </c>
       <c r="E42">
-        <v>-7.64</v>
+        <v>3.24</v>
       </c>
       <c r="F42" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="43">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D43">
-        <v>580.99</v>
+        <v>581.67</v>
       </c>
       <c r="E43">
-        <v>-0.12</v>
+        <v>-7.64</v>
       </c>
       <c r="F43" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="44">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D44">
-        <v>588.79</v>
+        <v>580.99</v>
       </c>
       <c r="E44">
-        <v>1.34</v>
+        <v>-0.12</v>
       </c>
       <c r="F44" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="45">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D45">
-        <v>554.67</v>
+        <v>588.79</v>
       </c>
       <c r="E45">
-        <v>-5.8</v>
+        <v>1.34</v>
       </c>
       <c r="F45" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="46">
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D46">
-        <v>591.6</v>
+        <v>554.67</v>
       </c>
       <c r="E46">
-        <v>6.66</v>
+        <v>-5.8</v>
       </c>
       <c r="F46" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="47">
@@ -1525,17 +1525,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D47">
-        <v>565.35</v>
+        <v>591.6</v>
       </c>
       <c r="E47">
-        <v>-4.44</v>
+        <v>6.66</v>
       </c>
       <c r="F47" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="48">
@@ -1546,22 +1546,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="D48">
-        <v>585.25</v>
+        <v>565.35</v>
       </c>
       <c r="E48">
-        <v>3.52</v>
+        <v>-4.44</v>
       </c>
       <c r="F48" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="49">
@@ -1577,17 +1577,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="D49">
-        <v>610.33</v>
+        <v>585.25</v>
       </c>
       <c r="E49">
-        <v>4.28</v>
+        <v>3.52</v>
       </c>
       <c r="F49" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="50">
@@ -1603,17 +1603,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="D50">
-        <v>615.97</v>
+        <v>610.33</v>
       </c>
       <c r="E50">
-        <v>0.92</v>
+        <v>4.28</v>
       </c>
       <c r="F50" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="51">
@@ -1629,11 +1629,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Abril</t>
-        </is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="D51">
+        <v>615.97</v>
+      </c>
+      <c r="E51">
+        <v>0.92</v>
       </c>
       <c r="F51" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="52">
@@ -1649,11 +1655,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="F52" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="53">
@@ -1669,11 +1675,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="F53" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="54">
@@ -1689,11 +1695,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="F54" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="55">
@@ -1709,11 +1715,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="F55" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="56">
@@ -1729,11 +1735,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="F56" s="2">
-        <v>45901</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="57">
@@ -1749,11 +1755,286 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="F57" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>Outubro</t>
         </is>
       </c>
-      <c r="F57" s="2">
+      <c r="F58" s="2">
         <v>45931</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
+      <c r="F59" s="2">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="F60" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="F61" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="F62" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="F63" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="F64" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="F65" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="F66" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="F67" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D68">
+        <v>648.5700000000001</v>
+      </c>
+      <c r="F68" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="D69">
+        <v>628.83</v>
+      </c>
+      <c r="E69">
+        <v>-3.04</v>
+      </c>
+      <c r="F69" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
+      <c r="D70">
+        <v>625.33</v>
+      </c>
+      <c r="E70">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="F70" s="2">
+        <v>45962</v>
       </c>
     </row>
   </sheetData>

--- a/CT.xlsx
+++ b/CT.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -1264,21 +1264,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Janeiro</t>
-        </is>
+          <t>Dezembro</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>639.74</v>
+      </c>
+      <c r="E37">
+        <v>0.32</v>
       </c>
       <c r="F37" s="2">
-        <v>45292</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="38">
@@ -1294,14 +1300,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
-        </is>
-      </c>
-      <c r="D38">
-        <v>596.15</v>
+          <t>Janeiro</t>
+        </is>
       </c>
       <c r="F38" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="39">
@@ -1317,17 +1320,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="D39">
-        <v>635.98</v>
-      </c>
-      <c r="E39">
-        <v>6.68</v>
+        <v>596.15</v>
       </c>
       <c r="F39" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="40">
@@ -1343,17 +1343,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D40">
-        <v>619.71</v>
+        <v>635.98</v>
       </c>
       <c r="E40">
-        <v>-2.56</v>
+        <v>6.68</v>
       </c>
       <c r="F40" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="41">
@@ -1369,17 +1369,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D41">
-        <v>610.02</v>
+        <v>619.71</v>
       </c>
       <c r="E41">
-        <v>-1.56</v>
+        <v>-2.56</v>
       </c>
       <c r="F41" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="42">
@@ -1395,17 +1395,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D42">
-        <v>629.77</v>
+        <v>610.02</v>
       </c>
       <c r="E42">
-        <v>3.24</v>
+        <v>-1.56</v>
       </c>
       <c r="F42" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="43">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D43">
-        <v>581.67</v>
+        <v>629.77</v>
       </c>
       <c r="E43">
-        <v>-7.64</v>
+        <v>3.24</v>
       </c>
       <c r="F43" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="44">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D44">
-        <v>580.99</v>
+        <v>581.67</v>
       </c>
       <c r="E44">
-        <v>-0.12</v>
+        <v>-7.64</v>
       </c>
       <c r="F44" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="45">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D45">
-        <v>588.79</v>
+        <v>580.99</v>
       </c>
       <c r="E45">
-        <v>1.34</v>
+        <v>-0.12</v>
       </c>
       <c r="F45" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="46">
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D46">
-        <v>554.67</v>
+        <v>588.79</v>
       </c>
       <c r="E46">
-        <v>-5.8</v>
+        <v>1.34</v>
       </c>
       <c r="F46" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="47">
@@ -1525,17 +1525,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D47">
-        <v>591.6</v>
+        <v>554.67</v>
       </c>
       <c r="E47">
-        <v>6.66</v>
+        <v>-5.8</v>
       </c>
       <c r="F47" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="48">
@@ -1551,17 +1551,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D48">
-        <v>565.35</v>
+        <v>591.6</v>
       </c>
       <c r="E48">
-        <v>-4.44</v>
+        <v>6.66</v>
       </c>
       <c r="F48" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="49">
@@ -1572,22 +1572,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="D49">
-        <v>585.25</v>
+        <v>565.35</v>
       </c>
       <c r="E49">
-        <v>3.52</v>
+        <v>-4.44</v>
       </c>
       <c r="F49" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="50">
@@ -1603,17 +1603,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="D50">
-        <v>610.33</v>
+        <v>585.25</v>
       </c>
       <c r="E50">
-        <v>4.28</v>
+        <v>3.52</v>
       </c>
       <c r="F50" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="51">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="D51">
-        <v>615.97</v>
+        <v>610.33</v>
       </c>
       <c r="E51">
-        <v>0.92</v>
+        <v>4.28</v>
       </c>
       <c r="F51" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="52">
@@ -1655,11 +1655,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Abril</t>
-        </is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="D52">
+        <v>615.97</v>
+      </c>
+      <c r="E52">
+        <v>0.92</v>
       </c>
       <c r="F52" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="53">
@@ -1675,11 +1681,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="F53" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="54">
@@ -1695,11 +1701,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="F54" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="55">
@@ -1715,11 +1721,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="F55" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="56">
@@ -1735,11 +1741,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="F56" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="57">
@@ -1755,11 +1761,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="F57" s="2">
-        <v>45901</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="58">
@@ -1775,11 +1781,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="F58" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="59">
@@ -1795,17 +1801,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="F59" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1815,17 +1821,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="F60" s="2">
-        <v>45658</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1835,11 +1841,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="F61" s="2">
-        <v>45689</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="62">
@@ -1855,11 +1861,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="F62" s="2">
-        <v>45717</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="63">
@@ -1875,11 +1881,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="F63" s="2">
-        <v>45748</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="64">
@@ -1895,11 +1901,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="F64" s="2">
-        <v>45778</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="65">
@@ -1915,11 +1921,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="F65" s="2">
-        <v>45809</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="66">
@@ -1935,11 +1941,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="F66" s="2">
-        <v>45839</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="67">
@@ -1955,11 +1961,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="F67" s="2">
-        <v>45870</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="68">
@@ -1975,14 +1981,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Setembro</t>
-        </is>
-      </c>
-      <c r="D68">
-        <v>648.5700000000001</v>
+          <t>Julho</t>
+        </is>
       </c>
       <c r="F68" s="2">
-        <v>45901</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="69">
@@ -1998,17 +2001,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Outubro</t>
-        </is>
-      </c>
-      <c r="D69">
-        <v>628.83</v>
-      </c>
-      <c r="E69">
-        <v>-3.04</v>
+          <t>Agosto</t>
+        </is>
       </c>
       <c r="F69" s="2">
-        <v>45931</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="70">
@@ -2024,17 +2021,86 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D70">
+        <v>648.5700000000001</v>
+      </c>
+      <c r="F70" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="D71">
+        <v>628.83</v>
+      </c>
+      <c r="E71">
+        <v>-3.04</v>
+      </c>
+      <c r="F71" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
           <t>Novembro</t>
         </is>
       </c>
-      <c r="D70">
+      <c r="D72">
         <v>625.33</v>
       </c>
-      <c r="E70">
+      <c r="E72">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F72" s="2">
         <v>45962</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Dezembro</t>
+        </is>
+      </c>
+      <c r="F73" s="2">
+        <v>45992</v>
       </c>
     </row>
   </sheetData>

--- a/CT.xlsx
+++ b/CT.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -1290,12 +1290,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1303,19 +1303,25 @@
           <t>Janeiro</t>
         </is>
       </c>
+      <c r="D38">
+        <v>652.98</v>
+      </c>
+      <c r="E38">
+        <v>2.07</v>
+      </c>
       <c r="F38" s="2">
-        <v>45292</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1323,11 +1329,8 @@
           <t>Fevereiro</t>
         </is>
       </c>
-      <c r="D39">
-        <v>596.15</v>
-      </c>
       <c r="F39" s="2">
-        <v>45323</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="40">
@@ -1343,17 +1346,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Março</t>
-        </is>
-      </c>
-      <c r="D40">
-        <v>635.98</v>
-      </c>
-      <c r="E40">
-        <v>6.68</v>
+          <t>Janeiro</t>
+        </is>
       </c>
       <c r="F40" s="2">
-        <v>45352</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="41">
@@ -1369,17 +1366,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="D41">
-        <v>619.71</v>
-      </c>
-      <c r="E41">
-        <v>-2.56</v>
+        <v>596.15</v>
       </c>
       <c r="F41" s="2">
-        <v>45383</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="42">
@@ -1395,17 +1389,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D42">
-        <v>610.02</v>
+        <v>635.98</v>
       </c>
       <c r="E42">
-        <v>-1.56</v>
+        <v>6.68</v>
       </c>
       <c r="F42" s="2">
-        <v>45413</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="43">
@@ -1421,17 +1415,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D43">
-        <v>629.77</v>
+        <v>619.71</v>
       </c>
       <c r="E43">
-        <v>3.24</v>
+        <v>-2.56</v>
       </c>
       <c r="F43" s="2">
-        <v>45444</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="44">
@@ -1447,17 +1441,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D44">
-        <v>581.67</v>
+        <v>610.02</v>
       </c>
       <c r="E44">
-        <v>-7.64</v>
+        <v>-1.56</v>
       </c>
       <c r="F44" s="2">
-        <v>45474</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="45">
@@ -1473,17 +1467,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D45">
-        <v>580.99</v>
+        <v>629.77</v>
       </c>
       <c r="E45">
-        <v>-0.12</v>
+        <v>3.24</v>
       </c>
       <c r="F45" s="2">
-        <v>45505</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="46">
@@ -1499,17 +1493,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D46">
-        <v>588.79</v>
+        <v>581.67</v>
       </c>
       <c r="E46">
-        <v>1.34</v>
+        <v>-7.64</v>
       </c>
       <c r="F46" s="2">
-        <v>45536</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="47">
@@ -1525,17 +1519,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D47">
-        <v>554.67</v>
+        <v>580.99</v>
       </c>
       <c r="E47">
-        <v>-5.8</v>
+        <v>-0.12</v>
       </c>
       <c r="F47" s="2">
-        <v>45566</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="48">
@@ -1551,17 +1545,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D48">
-        <v>591.6</v>
+        <v>588.79</v>
       </c>
       <c r="E48">
-        <v>6.66</v>
+        <v>1.34</v>
       </c>
       <c r="F48" s="2">
-        <v>45597</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="49">
@@ -1577,17 +1571,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D49">
-        <v>565.35</v>
+        <v>554.67</v>
       </c>
       <c r="E49">
-        <v>-4.44</v>
+        <v>-5.8</v>
       </c>
       <c r="F49" s="2">
-        <v>45627</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="50">
@@ -1598,22 +1592,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D50">
-        <v>585.25</v>
+        <v>591.6</v>
       </c>
       <c r="E50">
-        <v>3.52</v>
+        <v>6.66</v>
       </c>
       <c r="F50" s="2">
-        <v>45658</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="51">
@@ -1624,22 +1618,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="D51">
-        <v>610.33</v>
+        <v>565.35</v>
       </c>
       <c r="E51">
-        <v>4.28</v>
+        <v>-4.44</v>
       </c>
       <c r="F51" s="2">
-        <v>45689</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="52">
@@ -1655,17 +1649,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="D52">
-        <v>615.97</v>
+        <v>585.25</v>
       </c>
       <c r="E52">
-        <v>0.92</v>
+        <v>3.52</v>
       </c>
       <c r="F52" s="2">
-        <v>45717</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="53">
@@ -1681,11 +1675,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Abril</t>
-        </is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="D53">
+        <v>610.33</v>
+      </c>
+      <c r="E53">
+        <v>4.28</v>
       </c>
       <c r="F53" s="2">
-        <v>45748</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="54">
@@ -1701,11 +1701,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Maio</t>
-        </is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="D54">
+        <v>615.97</v>
+      </c>
+      <c r="E54">
+        <v>0.92</v>
       </c>
       <c r="F54" s="2">
-        <v>45778</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="55">
@@ -1721,11 +1727,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="F55" s="2">
-        <v>45809</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="56">
@@ -1741,11 +1747,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="F56" s="2">
-        <v>45839</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="57">
@@ -1761,11 +1767,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="F57" s="2">
-        <v>45870</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="58">
@@ -1781,11 +1787,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="F58" s="2">
-        <v>45901</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="59">
@@ -1801,11 +1807,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="F59" s="2">
-        <v>45931</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="60">
@@ -1821,11 +1827,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="F60" s="2">
-        <v>45962</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="61">
@@ -1841,17 +1847,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="F61" s="2">
-        <v>45992</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1861,17 +1867,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="F62" s="2">
-        <v>45658</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1881,11 +1887,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="F63" s="2">
-        <v>45689</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="64">
@@ -1901,11 +1907,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="F64" s="2">
-        <v>45717</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="65">
@@ -1921,11 +1927,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="F65" s="2">
-        <v>45748</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="66">
@@ -1941,11 +1947,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="F66" s="2">
-        <v>45778</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="67">
@@ -1961,11 +1967,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="F67" s="2">
-        <v>45809</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="68">
@@ -1981,11 +1987,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="F68" s="2">
-        <v>45839</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="69">
@@ -2001,11 +2007,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="F69" s="2">
-        <v>45870</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="70">
@@ -2021,14 +2027,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Setembro</t>
-        </is>
-      </c>
-      <c r="D70">
-        <v>648.5700000000001</v>
+          <t>Julho</t>
+        </is>
       </c>
       <c r="F70" s="2">
-        <v>45901</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="71">
@@ -2044,17 +2047,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Outubro</t>
-        </is>
-      </c>
-      <c r="D71">
-        <v>628.83</v>
-      </c>
-      <c r="E71">
-        <v>-3.04</v>
+          <t>Agosto</t>
+        </is>
       </c>
       <c r="F71" s="2">
-        <v>45931</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="72">
@@ -2070,17 +2067,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D72">
-        <v>625.33</v>
-      </c>
-      <c r="E72">
-        <v>-0.5600000000000001</v>
+        <v>648.5700000000001</v>
       </c>
       <c r="F72" s="2">
-        <v>45962</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="73">
@@ -2096,10 +2090,62 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="D73">
+        <v>628.83</v>
+      </c>
+      <c r="E73">
+        <v>-3.04</v>
+      </c>
+      <c r="F73" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
+      <c r="D74">
+        <v>625.33</v>
+      </c>
+      <c r="E74">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="F74" s="2">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
           <t>Dezembro</t>
         </is>
       </c>
-      <c r="F73" s="2">
+      <c r="F75" s="2">
         <v>45992</v>
       </c>
     </row>

--- a/CT.xlsx
+++ b/CT.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -1336,44 +1336,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Janeiro</t>
-        </is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="D40">
+        <v>620.11</v>
       </c>
       <c r="F40" s="2">
-        <v>45292</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D41">
-        <v>596.15</v>
+        <v>615.78</v>
+      </c>
+      <c r="E41">
+        <v>-0.7</v>
       </c>
       <c r="F41" s="2">
-        <v>45323</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="42">
@@ -1389,17 +1395,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Março</t>
-        </is>
-      </c>
-      <c r="D42">
-        <v>635.98</v>
-      </c>
-      <c r="E42">
-        <v>6.68</v>
+          <t>Janeiro</t>
+        </is>
       </c>
       <c r="F42" s="2">
-        <v>45352</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="43">
@@ -1415,17 +1415,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="D43">
-        <v>619.71</v>
-      </c>
-      <c r="E43">
-        <v>-2.56</v>
+        <v>596.15</v>
       </c>
       <c r="F43" s="2">
-        <v>45383</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="44">
@@ -1441,17 +1438,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D44">
-        <v>610.02</v>
+        <v>635.98</v>
       </c>
       <c r="E44">
-        <v>-1.56</v>
+        <v>6.68</v>
       </c>
       <c r="F44" s="2">
-        <v>45413</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="45">
@@ -1467,17 +1464,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D45">
-        <v>629.77</v>
+        <v>619.71</v>
       </c>
       <c r="E45">
-        <v>3.24</v>
+        <v>-2.56</v>
       </c>
       <c r="F45" s="2">
-        <v>45444</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="46">
@@ -1493,17 +1490,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D46">
-        <v>581.67</v>
+        <v>610.02</v>
       </c>
       <c r="E46">
-        <v>-7.64</v>
+        <v>-1.56</v>
       </c>
       <c r="F46" s="2">
-        <v>45474</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="47">
@@ -1519,17 +1516,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D47">
-        <v>580.99</v>
+        <v>629.77</v>
       </c>
       <c r="E47">
-        <v>-0.12</v>
+        <v>3.24</v>
       </c>
       <c r="F47" s="2">
-        <v>45505</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="48">
@@ -1545,17 +1542,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D48">
-        <v>588.79</v>
+        <v>581.67</v>
       </c>
       <c r="E48">
-        <v>1.34</v>
+        <v>-7.64</v>
       </c>
       <c r="F48" s="2">
-        <v>45536</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="49">
@@ -1571,17 +1568,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D49">
-        <v>554.67</v>
+        <v>580.99</v>
       </c>
       <c r="E49">
-        <v>-5.8</v>
+        <v>-0.12</v>
       </c>
       <c r="F49" s="2">
-        <v>45566</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="50">
@@ -1597,17 +1594,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D50">
-        <v>591.6</v>
+        <v>588.79</v>
       </c>
       <c r="E50">
-        <v>6.66</v>
+        <v>1.34</v>
       </c>
       <c r="F50" s="2">
-        <v>45597</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="51">
@@ -1623,17 +1620,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D51">
-        <v>565.35</v>
+        <v>554.67</v>
       </c>
       <c r="E51">
-        <v>-4.44</v>
+        <v>-5.8</v>
       </c>
       <c r="F51" s="2">
-        <v>45627</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="52">
@@ -1644,22 +1641,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D52">
-        <v>585.25</v>
+        <v>591.6</v>
       </c>
       <c r="E52">
-        <v>3.52</v>
+        <v>6.66</v>
       </c>
       <c r="F52" s="2">
-        <v>45658</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="53">
@@ -1670,22 +1667,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="D53">
-        <v>610.33</v>
+        <v>565.35</v>
       </c>
       <c r="E53">
-        <v>4.28</v>
+        <v>-4.44</v>
       </c>
       <c r="F53" s="2">
-        <v>45689</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="54">
@@ -1701,17 +1698,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="D54">
-        <v>615.97</v>
+        <v>585.25</v>
       </c>
       <c r="E54">
-        <v>0.92</v>
+        <v>3.52</v>
       </c>
       <c r="F54" s="2">
-        <v>45717</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="55">
@@ -1727,11 +1724,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Abril</t>
-        </is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="D55">
+        <v>610.33</v>
+      </c>
+      <c r="E55">
+        <v>4.28</v>
       </c>
       <c r="F55" s="2">
-        <v>45748</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="56">
@@ -1747,11 +1750,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Maio</t>
-        </is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="D56">
+        <v>615.97</v>
+      </c>
+      <c r="E56">
+        <v>0.92</v>
       </c>
       <c r="F56" s="2">
-        <v>45778</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="57">
@@ -1767,11 +1776,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="F57" s="2">
-        <v>45809</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="58">
@@ -1787,11 +1796,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="F58" s="2">
-        <v>45839</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="59">
@@ -1807,11 +1816,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="F59" s="2">
-        <v>45870</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="60">
@@ -1827,11 +1836,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="F60" s="2">
-        <v>45901</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="61">
@@ -1847,11 +1856,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="F61" s="2">
-        <v>45931</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="62">
@@ -1867,11 +1876,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="F62" s="2">
-        <v>45962</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="63">
@@ -1887,17 +1896,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="F63" s="2">
-        <v>45992</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1907,17 +1916,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="F64" s="2">
-        <v>45658</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1927,11 +1936,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="F65" s="2">
-        <v>45689</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="66">
@@ -1947,11 +1956,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="F66" s="2">
-        <v>45717</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="67">
@@ -1967,11 +1976,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="F67" s="2">
-        <v>45748</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="68">
@@ -1987,11 +1996,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="F68" s="2">
-        <v>45778</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="69">
@@ -2007,11 +2016,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="F69" s="2">
-        <v>45809</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="70">
@@ -2027,11 +2036,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="F70" s="2">
-        <v>45839</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="71">
@@ -2047,11 +2056,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="F71" s="2">
-        <v>45870</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="72">
@@ -2067,14 +2076,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Setembro</t>
-        </is>
-      </c>
-      <c r="D72">
-        <v>648.5700000000001</v>
+          <t>Julho</t>
+        </is>
       </c>
       <c r="F72" s="2">
-        <v>45901</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="73">
@@ -2090,17 +2096,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Outubro</t>
-        </is>
-      </c>
-      <c r="D73">
-        <v>628.83</v>
-      </c>
-      <c r="E73">
-        <v>-3.04</v>
+          <t>Agosto</t>
+        </is>
       </c>
       <c r="F73" s="2">
-        <v>45931</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="74">
@@ -2116,17 +2116,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D74">
-        <v>625.33</v>
-      </c>
-      <c r="E74">
-        <v>-0.5600000000000001</v>
+        <v>648.5700000000001</v>
       </c>
       <c r="F74" s="2">
-        <v>45962</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="75">
@@ -2142,10 +2139,62 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="D75">
+        <v>628.83</v>
+      </c>
+      <c r="E75">
+        <v>-3.04</v>
+      </c>
+      <c r="F75" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
+      <c r="D76">
+        <v>625.33</v>
+      </c>
+      <c r="E76">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="F76" s="2">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
           <t>Dezembro</t>
         </is>
       </c>
-      <c r="F75" s="2">
+      <c r="F77" s="2">
         <v>45992</v>
       </c>
     </row>

--- a/CT.xlsx
+++ b/CT.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="D41">
-        <v>615.78</v>
+        <v>624.02</v>
       </c>
       <c r="E41">
-        <v>-0.7</v>
+        <v>0.63</v>
       </c>
       <c r="F41" s="2">
         <v>46113</v>
@@ -1385,21 +1385,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Janeiro</t>
-        </is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>600.64</v>
+      </c>
+      <c r="E42">
+        <v>-3.75</v>
       </c>
       <c r="F42" s="2">
-        <v>45292</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="43">
@@ -1415,14 +1421,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
-        </is>
-      </c>
-      <c r="D43">
-        <v>596.15</v>
+          <t>Janeiro</t>
+        </is>
       </c>
       <c r="F43" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="44">
@@ -1438,17 +1441,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="D44">
-        <v>635.98</v>
-      </c>
-      <c r="E44">
-        <v>6.68</v>
+        <v>596.15</v>
       </c>
       <c r="F44" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="45">
@@ -1464,17 +1464,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D45">
-        <v>619.71</v>
+        <v>635.98</v>
       </c>
       <c r="E45">
-        <v>-2.56</v>
+        <v>6.68</v>
       </c>
       <c r="F45" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="46">
@@ -1490,17 +1490,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D46">
-        <v>610.02</v>
+        <v>619.71</v>
       </c>
       <c r="E46">
-        <v>-1.56</v>
+        <v>-2.56</v>
       </c>
       <c r="F46" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="47">
@@ -1516,17 +1516,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D47">
-        <v>629.77</v>
+        <v>610.02</v>
       </c>
       <c r="E47">
-        <v>3.24</v>
+        <v>-1.56</v>
       </c>
       <c r="F47" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="48">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D48">
-        <v>581.67</v>
+        <v>629.77</v>
       </c>
       <c r="E48">
-        <v>-7.64</v>
+        <v>3.24</v>
       </c>
       <c r="F48" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="49">
@@ -1568,17 +1568,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D49">
-        <v>580.99</v>
+        <v>581.67</v>
       </c>
       <c r="E49">
-        <v>-0.12</v>
+        <v>-7.64</v>
       </c>
       <c r="F49" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="50">
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D50">
-        <v>588.79</v>
+        <v>580.99</v>
       </c>
       <c r="E50">
-        <v>1.34</v>
+        <v>-0.12</v>
       </c>
       <c r="F50" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="51">
@@ -1620,17 +1620,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D51">
-        <v>554.67</v>
+        <v>588.79</v>
       </c>
       <c r="E51">
-        <v>-5.8</v>
+        <v>1.34</v>
       </c>
       <c r="F51" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="52">
@@ -1646,17 +1646,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D52">
-        <v>591.6</v>
+        <v>554.67</v>
       </c>
       <c r="E52">
-        <v>6.66</v>
+        <v>-5.8</v>
       </c>
       <c r="F52" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="53">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D53">
-        <v>565.35</v>
+        <v>591.6</v>
       </c>
       <c r="E53">
-        <v>-4.44</v>
+        <v>6.66</v>
       </c>
       <c r="F53" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="54">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="D54">
-        <v>585.25</v>
+        <v>565.35</v>
       </c>
       <c r="E54">
-        <v>3.52</v>
+        <v>-4.44</v>
       </c>
       <c r="F54" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="55">
@@ -1724,17 +1724,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="D55">
-        <v>610.33</v>
+        <v>585.25</v>
       </c>
       <c r="E55">
-        <v>4.28</v>
+        <v>3.52</v>
       </c>
       <c r="F55" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="56">
@@ -1750,17 +1750,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="D56">
-        <v>615.97</v>
+        <v>610.33</v>
       </c>
       <c r="E56">
-        <v>0.92</v>
+        <v>4.28</v>
       </c>
       <c r="F56" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="57">
@@ -1776,11 +1776,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Abril</t>
-        </is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="D57">
+        <v>615.97</v>
+      </c>
+      <c r="E57">
+        <v>0.92</v>
       </c>
       <c r="F57" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="58">
@@ -1796,11 +1802,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="F58" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="59">
@@ -1816,11 +1822,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="F59" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="60">
@@ -1836,11 +1842,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="F60" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="61">
@@ -1856,11 +1862,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="F61" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="62">
@@ -1876,11 +1882,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="F62" s="2">
-        <v>45901</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="63">
@@ -1896,11 +1902,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="F63" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="64">
@@ -1916,11 +1922,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="F64" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="65">
@@ -1936,17 +1942,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="F65" s="2">
-        <v>45992</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1956,11 +1962,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="F66" s="2">
-        <v>45658</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="67">
@@ -1976,11 +1982,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="F67" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="68">
@@ -1996,11 +2002,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="F68" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="69">
@@ -2016,11 +2022,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="F69" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="70">
@@ -2036,11 +2042,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="F70" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="71">
@@ -2056,11 +2062,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="F71" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="72">
@@ -2076,11 +2082,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="F72" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="73">
@@ -2096,11 +2102,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="F73" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="74">
@@ -2116,14 +2122,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Setembro</t>
-        </is>
-      </c>
-      <c r="D74">
-        <v>648.5700000000001</v>
+          <t>Agosto</t>
+        </is>
       </c>
       <c r="F74" s="2">
-        <v>45901</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="75">
@@ -2139,17 +2142,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D75">
-        <v>628.83</v>
-      </c>
-      <c r="E75">
-        <v>-3.04</v>
+        <v>648.5700000000001</v>
       </c>
       <c r="F75" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="76">
@@ -2165,17 +2165,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D76">
-        <v>625.33</v>
+        <v>628.83</v>
       </c>
       <c r="E76">
-        <v>-0.5600000000000001</v>
+        <v>-3.04</v>
       </c>
       <c r="F76" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="77">
@@ -2191,10 +2191,36 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
+          <t>Novembro</t>
+        </is>
+      </c>
+      <c r="D77">
+        <v>625.33</v>
+      </c>
+      <c r="E77">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="F77" s="2">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
           <t>Dezembro</t>
         </is>
       </c>
-      <c r="F77" s="2">
+      <c r="F78" s="2">
         <v>45992</v>
       </c>
     </row>

--- a/CT.xlsx
+++ b/CT.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="D44">
-        <v>596.15</v>
+        <v>614.34</v>
       </c>
       <c r="F44" s="2">
         <v>45323</v>
@@ -1471,7 +1471,7 @@
         <v>635.98</v>
       </c>
       <c r="E45">
-        <v>6.68</v>
+        <v>3.52</v>
       </c>
       <c r="F45" s="2">
         <v>45352</v>
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="D51">
-        <v>588.79</v>
+        <v>568.29</v>
       </c>
       <c r="E51">
-        <v>1.34</v>
+        <v>-2.19</v>
       </c>
       <c r="F51" s="2">
         <v>45536</v>
@@ -1653,7 +1653,7 @@
         <v>554.67</v>
       </c>
       <c r="E52">
-        <v>-5.8</v>
+        <v>-2.4</v>
       </c>
       <c r="F52" s="2">
         <v>45566</v>
@@ -1972,12 +1972,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1986,18 +1986,18 @@
         </is>
       </c>
       <c r="F67" s="2">
-        <v>45658</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2006,18 +2006,18 @@
         </is>
       </c>
       <c r="F68" s="2">
-        <v>45689</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2025,19 +2025,22 @@
           <t>Março</t>
         </is>
       </c>
+      <c r="D69">
+        <v>584.04</v>
+      </c>
       <c r="F69" s="2">
-        <v>45717</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2045,19 +2048,25 @@
           <t>Abril</t>
         </is>
       </c>
+      <c r="D70">
+        <v>618.51</v>
+      </c>
+      <c r="E70">
+        <v>5.9</v>
+      </c>
       <c r="F70" s="2">
-        <v>45748</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2065,8 +2074,14 @@
           <t>Maio</t>
         </is>
       </c>
+      <c r="D71">
+        <v>648.72</v>
+      </c>
+      <c r="E71">
+        <v>4.88</v>
+      </c>
       <c r="F71" s="2">
-        <v>45778</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="72">
@@ -2082,11 +2097,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="F72" s="2">
-        <v>45809</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="73">
@@ -2102,11 +2117,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="F73" s="2">
-        <v>45839</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="74">
@@ -2122,11 +2137,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="F74" s="2">
-        <v>45870</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="75">
@@ -2142,14 +2157,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Setembro</t>
-        </is>
-      </c>
-      <c r="D75">
-        <v>648.5700000000001</v>
+          <t>Abril</t>
+        </is>
       </c>
       <c r="F75" s="2">
-        <v>45901</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="76">
@@ -2165,17 +2177,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Outubro</t>
-        </is>
-      </c>
-      <c r="D76">
-        <v>628.83</v>
-      </c>
-      <c r="E76">
-        <v>-3.04</v>
+          <t>Maio</t>
+        </is>
       </c>
       <c r="F76" s="2">
-        <v>45931</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="77">
@@ -2191,17 +2197,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Novembro</t>
-        </is>
-      </c>
-      <c r="D77">
-        <v>625.33</v>
-      </c>
-      <c r="E77">
-        <v>-0.5600000000000001</v>
+          <t>Junho</t>
+        </is>
       </c>
       <c r="F77" s="2">
-        <v>45962</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="78">
@@ -2217,11 +2217,771 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="F78" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="F79" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D80">
+        <v>648.5700000000001</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="D81">
+        <v>648.67</v>
+      </c>
+      <c r="E81">
+        <v>0.02</v>
+      </c>
+      <c r="F81" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
+      <c r="D82">
+        <v>625.33</v>
+      </c>
+      <c r="E82">
+        <v>-3.6</v>
+      </c>
+      <c r="F82" s="2">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
           <t>Dezembro</t>
         </is>
       </c>
-      <c r="F78" s="2">
+      <c r="F83" s="2">
         <v>45992</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D84">
+        <v>616.47</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Bombinhas</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="F85" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Bombinhas</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="F86" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Bombinhas</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="D87">
+        <v>675.28</v>
+      </c>
+      <c r="F87" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Bombinhas</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D88">
+        <v>717.09</v>
+      </c>
+      <c r="E88">
+        <v>6.19</v>
+      </c>
+      <c r="F88" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Bombinhas</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="F89" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Indaial</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="F90" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Indaial</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="F91" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Indaial</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="F92" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Indaial</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D93">
+        <v>702.88</v>
+      </c>
+      <c r="F93" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Indaial</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="F94" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Jaraguá do Sul</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="F95" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Jaraguá do Sul</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="F96" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Jaraguá do Sul</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="D97">
+        <v>695.09</v>
+      </c>
+      <c r="F97" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Jaraguá do Sul</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D98">
+        <v>726.99</v>
+      </c>
+      <c r="E98">
+        <v>4.59</v>
+      </c>
+      <c r="F98" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Jaraguá do Sul</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="F99" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Massaranduba</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="F100" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Massaranduba</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="F101" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Massaranduba</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="F102" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Massaranduba</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D103">
+        <v>593.53</v>
+      </c>
+      <c r="F103" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Massaranduba</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="F104" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Navegantes</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="F105" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Navegantes</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="F106" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Navegantes</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="F107" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Navegantes</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D108">
+        <v>684.72</v>
+      </c>
+      <c r="F108" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Navegantes</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="F109" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="F110" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="F111" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="F112" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D113">
+        <v>760.12</v>
+      </c>
+      <c r="F113" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="F114" s="2">
+        <v>46143</v>
       </c>
     </row>
   </sheetData>

--- a/CT.xlsx
+++ b/CT.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -1411,21 +1411,21 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="F43" s="2">
-        <v>45292</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="44">
@@ -1441,14 +1441,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
-        </is>
-      </c>
-      <c r="D44">
-        <v>614.34</v>
+          <t>Janeiro</t>
+        </is>
       </c>
       <c r="F44" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="45">
@@ -1464,17 +1461,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="D45">
-        <v>635.98</v>
-      </c>
-      <c r="E45">
-        <v>3.52</v>
+        <v>614.34</v>
       </c>
       <c r="F45" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="46">
@@ -1490,17 +1484,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D46">
-        <v>619.71</v>
+        <v>635.98</v>
       </c>
       <c r="E46">
-        <v>-2.56</v>
+        <v>3.52</v>
       </c>
       <c r="F46" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="47">
@@ -1516,17 +1510,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D47">
-        <v>610.02</v>
+        <v>619.71</v>
       </c>
       <c r="E47">
-        <v>-1.56</v>
+        <v>-2.56</v>
       </c>
       <c r="F47" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="48">
@@ -1542,17 +1536,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D48">
-        <v>629.77</v>
+        <v>610.02</v>
       </c>
       <c r="E48">
-        <v>3.24</v>
+        <v>-1.56</v>
       </c>
       <c r="F48" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="49">
@@ -1568,17 +1562,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D49">
-        <v>581.67</v>
+        <v>629.77</v>
       </c>
       <c r="E49">
-        <v>-7.64</v>
+        <v>3.24</v>
       </c>
       <c r="F49" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="50">
@@ -1594,17 +1588,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D50">
-        <v>580.99</v>
+        <v>581.67</v>
       </c>
       <c r="E50">
-        <v>-0.12</v>
+        <v>-7.64</v>
       </c>
       <c r="F50" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="51">
@@ -1620,17 +1614,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D51">
-        <v>568.29</v>
+        <v>580.99</v>
       </c>
       <c r="E51">
-        <v>-2.19</v>
+        <v>-0.12</v>
       </c>
       <c r="F51" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="52">
@@ -1646,17 +1640,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D52">
-        <v>554.67</v>
+        <v>568.29</v>
       </c>
       <c r="E52">
-        <v>-2.4</v>
+        <v>-2.19</v>
       </c>
       <c r="F52" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="53">
@@ -1672,17 +1666,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D53">
-        <v>591.6</v>
+        <v>554.67</v>
       </c>
       <c r="E53">
-        <v>6.66</v>
+        <v>-2.4</v>
       </c>
       <c r="F53" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="54">
@@ -1698,17 +1692,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D54">
-        <v>565.35</v>
+        <v>591.6</v>
       </c>
       <c r="E54">
-        <v>-4.44</v>
+        <v>6.66</v>
       </c>
       <c r="F54" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="55">
@@ -1719,22 +1713,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="D55">
-        <v>585.25</v>
+        <v>565.35</v>
       </c>
       <c r="E55">
-        <v>3.52</v>
+        <v>-4.44</v>
       </c>
       <c r="F55" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="56">
@@ -1750,17 +1744,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="D56">
-        <v>610.33</v>
+        <v>585.25</v>
       </c>
       <c r="E56">
-        <v>4.28</v>
+        <v>3.52</v>
       </c>
       <c r="F56" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="57">
@@ -1776,17 +1770,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="D57">
-        <v>615.97</v>
+        <v>610.33</v>
       </c>
       <c r="E57">
-        <v>0.92</v>
+        <v>4.28</v>
       </c>
       <c r="F57" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="58">
@@ -1802,11 +1796,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Abril</t>
-        </is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="D58">
+        <v>615.97</v>
+      </c>
+      <c r="E58">
+        <v>0.92</v>
       </c>
       <c r="F58" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="59">
@@ -1822,11 +1822,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="F59" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="60">
@@ -1842,11 +1842,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="F60" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="61">
@@ -1862,11 +1862,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="F61" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="62">
@@ -1882,11 +1882,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="F62" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="63">
@@ -1902,11 +1902,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="F63" s="2">
-        <v>45901</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="64">
@@ -1922,11 +1922,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="F64" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="65">
@@ -1942,11 +1942,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="F65" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="66">
@@ -1962,11 +1962,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="F66" s="2">
-        <v>45992</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="67">
@@ -1977,16 +1977,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="F67" s="2">
-        <v>46023</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="68">
@@ -2002,11 +2002,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="F68" s="2">
-        <v>46054</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="69">
@@ -2022,14 +2022,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Março</t>
-        </is>
-      </c>
-      <c r="D69">
-        <v>584.04</v>
+          <t>Fevereiro</t>
+        </is>
       </c>
       <c r="F69" s="2">
-        <v>46082</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="70">
@@ -2045,17 +2042,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D70">
-        <v>618.51</v>
-      </c>
-      <c r="E70">
-        <v>5.9</v>
+        <v>584.04</v>
       </c>
       <c r="F70" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="71">
@@ -2071,57 +2065,63 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D71">
-        <v>648.72</v>
+        <v>618.51</v>
       </c>
       <c r="E71">
-        <v>4.88</v>
+        <v>5.9</v>
       </c>
       <c r="F71" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Janeiro</t>
-        </is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="D72">
+        <v>648.72</v>
+      </c>
+      <c r="E72">
+        <v>4.88</v>
       </c>
       <c r="F72" s="2">
-        <v>45658</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="F73" s="2">
-        <v>45689</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="74">
@@ -2137,11 +2137,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="F74" s="2">
-        <v>45717</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="75">
@@ -2157,11 +2157,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="F75" s="2">
-        <v>45748</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="76">
@@ -2177,11 +2177,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="F76" s="2">
-        <v>45778</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="77">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="F77" s="2">
-        <v>45809</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="78">
@@ -2217,11 +2217,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="F78" s="2">
-        <v>45839</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="79">
@@ -2237,11 +2237,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="F79" s="2">
-        <v>45870</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="80">
@@ -2257,14 +2257,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Setembro</t>
-        </is>
-      </c>
-      <c r="D80">
-        <v>648.5700000000001</v>
+          <t>Julho</t>
+        </is>
       </c>
       <c r="F80" s="2">
-        <v>45901</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="81">
@@ -2280,17 +2277,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Outubro</t>
-        </is>
-      </c>
-      <c r="D81">
-        <v>648.67</v>
-      </c>
-      <c r="E81">
-        <v>0.02</v>
+          <t>Agosto</t>
+        </is>
       </c>
       <c r="F81" s="2">
-        <v>45931</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="82">
@@ -2306,17 +2297,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D82">
-        <v>625.33</v>
-      </c>
-      <c r="E82">
-        <v>-3.6</v>
+        <v>648.5700000000001</v>
       </c>
       <c r="F82" s="2">
-        <v>45962</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="83">
@@ -2332,11 +2320,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dezembro</t>
-        </is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="D83">
+        <v>648.67</v>
+      </c>
+      <c r="E83">
+        <v>0.02</v>
       </c>
       <c r="F83" s="2">
-        <v>45992</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="84">
@@ -2350,48 +2344,54 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
       <c r="D84">
-        <v>616.47</v>
+        <v>625.33</v>
+      </c>
+      <c r="E84">
+        <v>-3.6</v>
+      </c>
+      <c r="F84" s="2">
+        <v>45962</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="F85" s="2">
-        <v>46023</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Fevereiro</t>
-        </is>
-      </c>
-      <c r="F86" s="2">
-        <v>46054</v>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D86">
+        <v>616.47</v>
       </c>
     </row>
     <row r="87">
@@ -2407,14 +2407,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Março</t>
-        </is>
-      </c>
-      <c r="D87">
-        <v>675.28</v>
+          <t>Janeiro</t>
+        </is>
       </c>
       <c r="F87" s="2">
-        <v>46082</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="88">
@@ -2430,17 +2427,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Abril</t>
-        </is>
-      </c>
-      <c r="D88">
-        <v>717.09</v>
-      </c>
-      <c r="E88">
-        <v>6.19</v>
+          <t>Fevereiro</t>
+        </is>
       </c>
       <c r="F88" s="2">
-        <v>46113</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="89">
@@ -2456,17 +2447,20 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Maio</t>
-        </is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="D89">
+        <v>675.28</v>
       </c>
       <c r="F89" s="2">
-        <v>46143</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2476,17 +2470,23 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Janeiro</t>
-        </is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D90">
+        <v>717.09</v>
+      </c>
+      <c r="E90">
+        <v>6.19</v>
       </c>
       <c r="F90" s="2">
-        <v>46023</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2496,17 +2496,23 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
-        </is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="D91">
+        <v>762.14</v>
+      </c>
+      <c r="E91">
+        <v>6.28</v>
       </c>
       <c r="F91" s="2">
-        <v>46054</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2516,11 +2522,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="F92" s="2">
-        <v>46082</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="93">
@@ -2536,14 +2542,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Abril</t>
-        </is>
-      </c>
-      <c r="D93">
-        <v>702.88</v>
+          <t>Janeiro</t>
+        </is>
       </c>
       <c r="F93" s="2">
-        <v>46113</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="94">
@@ -2559,17 +2562,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="F94" s="2">
-        <v>46143</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2579,17 +2582,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="F95" s="2">
-        <v>46023</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2599,17 +2602,20 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
-        </is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D96">
+        <v>702.88</v>
       </c>
       <c r="F96" s="2">
-        <v>46054</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2619,20 +2625,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Março</t>
-        </is>
-      </c>
-      <c r="D97">
-        <v>695.09</v>
+          <t>Maio</t>
+        </is>
       </c>
       <c r="F97" s="2">
-        <v>46082</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2642,17 +2645,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Abril</t>
-        </is>
-      </c>
-      <c r="D98">
-        <v>726.99</v>
-      </c>
-      <c r="E98">
-        <v>4.59</v>
+          <t>Junho</t>
+        </is>
       </c>
       <c r="F98" s="2">
-        <v>46113</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="99">
@@ -2668,17 +2665,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="F99" s="2">
-        <v>46143</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2688,17 +2685,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="F100" s="2">
-        <v>46023</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2708,17 +2705,20 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
-        </is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="D101">
+        <v>695.09</v>
       </c>
       <c r="F101" s="2">
-        <v>46054</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2728,17 +2728,23 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Março</t>
-        </is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D102">
+        <v>726.99</v>
+      </c>
+      <c r="E102">
+        <v>4.59</v>
       </c>
       <c r="F102" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2748,20 +2754,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Abril</t>
-        </is>
-      </c>
-      <c r="D103">
-        <v>593.53</v>
+          <t>Maio</t>
+        </is>
       </c>
       <c r="F103" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2771,17 +2774,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="F104" s="2">
-        <v>46143</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2801,7 +2804,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2821,7 +2824,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2841,7 +2844,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2855,7 +2858,7 @@
         </is>
       </c>
       <c r="D108">
-        <v>684.72</v>
+        <v>593.53</v>
       </c>
       <c r="F108" s="2">
         <v>46113</v>
@@ -2864,7 +2867,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2884,7 +2887,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2894,17 +2897,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="F110" s="2">
-        <v>46023</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2914,17 +2917,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="F111" s="2">
-        <v>46054</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2934,17 +2937,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="F112" s="2">
-        <v>46082</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2954,34 +2957,197 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Abril</t>
-        </is>
-      </c>
-      <c r="D113">
-        <v>760.12</v>
+          <t>Março</t>
+        </is>
       </c>
       <c r="F113" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>Navegantes</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D114">
+        <v>684.72</v>
+      </c>
+      <c r="F114" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Navegantes</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="F115" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Navegantes</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="F116" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
           <t>Timbó</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="F117" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="F118" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="F119" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D120">
+        <v>760.12</v>
+      </c>
+      <c r="F120" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
         <is>
           <t>Maio</t>
         </is>
       </c>
-      <c r="F114" s="2">
+      <c r="F121" s="2">
         <v>46143</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="F122" s="2">
+        <v>46174</v>
       </c>
     </row>
   </sheetData>

--- a/CT.xlsx
+++ b/CT.xlsx
@@ -1424,6 +1424,12 @@
           <t>Junho</t>
         </is>
       </c>
+      <c r="D43">
+        <v>706.49</v>
+      </c>
+      <c r="E43">
+        <v>17.62</v>
+      </c>
       <c r="F43" s="2">
         <v>46174</v>
       </c>

--- a/CT.xlsx
+++ b/CT.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F122"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="D43">
-        <v>706.49</v>
+        <v>640.46</v>
       </c>
       <c r="E43">
-        <v>17.62</v>
+        <v>6.63</v>
       </c>
       <c r="F43" s="2">
         <v>46174</v>
@@ -1437,44 +1437,41 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="F44" s="2">
-        <v>45292</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Gaspar</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
-        </is>
-      </c>
-      <c r="D45">
-        <v>614.34</v>
+          <t>Agosto</t>
+        </is>
       </c>
       <c r="F45" s="2">
-        <v>45323</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="46">
@@ -1490,17 +1487,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Março</t>
-        </is>
-      </c>
-      <c r="D46">
-        <v>635.98</v>
-      </c>
-      <c r="E46">
-        <v>3.52</v>
+          <t>Janeiro</t>
+        </is>
       </c>
       <c r="F46" s="2">
-        <v>45352</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="47">
@@ -1516,17 +1507,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="D47">
-        <v>619.71</v>
-      </c>
-      <c r="E47">
-        <v>-2.56</v>
+        <v>614.34</v>
       </c>
       <c r="F47" s="2">
-        <v>45383</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="48">
@@ -1542,17 +1530,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D48">
-        <v>610.02</v>
+        <v>635.98</v>
       </c>
       <c r="E48">
-        <v>-1.56</v>
+        <v>3.52</v>
       </c>
       <c r="F48" s="2">
-        <v>45413</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="49">
@@ -1568,17 +1556,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D49">
-        <v>629.77</v>
+        <v>619.71</v>
       </c>
       <c r="E49">
-        <v>3.24</v>
+        <v>-2.56</v>
       </c>
       <c r="F49" s="2">
-        <v>45444</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="50">
@@ -1594,17 +1582,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D50">
-        <v>581.67</v>
+        <v>610.02</v>
       </c>
       <c r="E50">
-        <v>-7.64</v>
+        <v>-1.56</v>
       </c>
       <c r="F50" s="2">
-        <v>45474</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="51">
@@ -1620,17 +1608,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D51">
-        <v>580.99</v>
+        <v>629.77</v>
       </c>
       <c r="E51">
-        <v>-0.12</v>
+        <v>3.24</v>
       </c>
       <c r="F51" s="2">
-        <v>45505</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="52">
@@ -1646,17 +1634,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D52">
-        <v>568.29</v>
+        <v>581.67</v>
       </c>
       <c r="E52">
-        <v>-2.19</v>
+        <v>-7.64</v>
       </c>
       <c r="F52" s="2">
-        <v>45536</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="53">
@@ -1672,17 +1660,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D53">
-        <v>554.67</v>
+        <v>580.99</v>
       </c>
       <c r="E53">
-        <v>-2.4</v>
+        <v>-0.12</v>
       </c>
       <c r="F53" s="2">
-        <v>45566</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="54">
@@ -1698,17 +1686,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D54">
-        <v>591.6</v>
+        <v>568.29</v>
       </c>
       <c r="E54">
-        <v>6.66</v>
+        <v>-2.19</v>
       </c>
       <c r="F54" s="2">
-        <v>45597</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="55">
@@ -1724,17 +1712,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D55">
-        <v>565.35</v>
+        <v>554.67</v>
       </c>
       <c r="E55">
-        <v>-4.44</v>
+        <v>-2.4</v>
       </c>
       <c r="F55" s="2">
-        <v>45627</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="56">
@@ -1745,22 +1733,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D56">
-        <v>585.25</v>
+        <v>591.6</v>
       </c>
       <c r="E56">
-        <v>3.52</v>
+        <v>6.66</v>
       </c>
       <c r="F56" s="2">
-        <v>45658</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="57">
@@ -1771,22 +1759,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="D57">
-        <v>610.33</v>
+        <v>565.35</v>
       </c>
       <c r="E57">
-        <v>4.28</v>
+        <v>-4.44</v>
       </c>
       <c r="F57" s="2">
-        <v>45689</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="58">
@@ -1802,17 +1790,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="D58">
-        <v>615.97</v>
+        <v>585.25</v>
       </c>
       <c r="E58">
-        <v>0.92</v>
+        <v>3.52</v>
       </c>
       <c r="F58" s="2">
-        <v>45717</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="59">
@@ -1828,11 +1816,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Abril</t>
-        </is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="D59">
+        <v>610.33</v>
+      </c>
+      <c r="E59">
+        <v>4.28</v>
       </c>
       <c r="F59" s="2">
-        <v>45748</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="60">
@@ -1848,11 +1842,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Maio</t>
-        </is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="D60">
+        <v>615.97</v>
+      </c>
+      <c r="E60">
+        <v>0.92</v>
       </c>
       <c r="F60" s="2">
-        <v>45778</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="61">
@@ -1868,11 +1868,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="F61" s="2">
-        <v>45809</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="62">
@@ -1888,11 +1888,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="F62" s="2">
-        <v>45839</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="63">
@@ -1908,11 +1908,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="F63" s="2">
-        <v>45870</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="64">
@@ -1928,11 +1928,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="F64" s="2">
-        <v>45901</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="65">
@@ -1948,11 +1948,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="F65" s="2">
-        <v>45931</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="66">
@@ -1968,11 +1968,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="F66" s="2">
-        <v>45962</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="67">
@@ -1988,11 +1988,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="F67" s="2">
-        <v>45992</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="68">
@@ -2003,16 +2003,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="F68" s="2">
-        <v>46023</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="69">
@@ -2023,16 +2023,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="F69" s="2">
-        <v>46054</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="70">
@@ -2048,14 +2048,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Março</t>
-        </is>
-      </c>
-      <c r="D70">
-        <v>584.04</v>
+          <t>Janeiro</t>
+        </is>
       </c>
       <c r="F70" s="2">
-        <v>46082</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="71">
@@ -2071,17 +2068,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Abril</t>
-        </is>
-      </c>
-      <c r="D71">
-        <v>618.51</v>
-      </c>
-      <c r="E71">
-        <v>5.9</v>
+          <t>Fevereiro</t>
+        </is>
       </c>
       <c r="F71" s="2">
-        <v>46113</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="72">
@@ -2097,17 +2088,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D72">
-        <v>648.72</v>
-      </c>
-      <c r="E72">
-        <v>4.88</v>
+        <v>584.04</v>
       </c>
       <c r="F72" s="2">
-        <v>46143</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="73">
@@ -2123,91 +2111,103 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Junho</t>
-        </is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D73">
+        <v>618.51</v>
+      </c>
+      <c r="E73">
+        <v>5.9</v>
       </c>
       <c r="F73" s="2">
-        <v>46174</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Janeiro</t>
-        </is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="D74">
+        <v>648.72</v>
+      </c>
+      <c r="E74">
+        <v>4.88</v>
       </c>
       <c r="F74" s="2">
-        <v>45658</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="F75" s="2">
-        <v>45689</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="F76" s="2">
-        <v>45717</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="F77" s="2">
-        <v>45748</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="78">
@@ -2223,11 +2223,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="F78" s="2">
-        <v>45778</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="79">
@@ -2243,11 +2243,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="F79" s="2">
-        <v>45809</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="80">
@@ -2263,11 +2263,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="F80" s="2">
-        <v>45839</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="81">
@@ -2283,11 +2283,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="F81" s="2">
-        <v>45870</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="82">
@@ -2303,14 +2303,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Setembro</t>
-        </is>
-      </c>
-      <c r="D82">
-        <v>648.5700000000001</v>
+          <t>Maio</t>
+        </is>
       </c>
       <c r="F82" s="2">
-        <v>45901</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="83">
@@ -2326,17 +2323,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Outubro</t>
-        </is>
-      </c>
-      <c r="D83">
-        <v>648.67</v>
-      </c>
-      <c r="E83">
-        <v>0.02</v>
+          <t>Junho</t>
+        </is>
       </c>
       <c r="F83" s="2">
-        <v>45931</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="84">
@@ -2352,17 +2343,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Novembro</t>
-        </is>
-      </c>
-      <c r="D84">
-        <v>625.33</v>
-      </c>
-      <c r="E84">
-        <v>-3.6</v>
+          <t>Julho</t>
+        </is>
       </c>
       <c r="F84" s="2">
-        <v>45962</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="85">
@@ -2378,11 +2363,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="F85" s="2">
-        <v>45992</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="86">
@@ -2396,103 +2381,109 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
       <c r="D86">
-        <v>616.47</v>
+        <v>648.5700000000001</v>
+      </c>
+      <c r="F86" s="2">
+        <v>45901</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Janeiro</t>
-        </is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="D87">
+        <v>648.67</v>
+      </c>
+      <c r="E87">
+        <v>0.02</v>
       </c>
       <c r="F87" s="2">
-        <v>46023</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
-        </is>
+          <t>Novembro</t>
+        </is>
+      </c>
+      <c r="D88">
+        <v>625.33</v>
+      </c>
+      <c r="E88">
+        <v>-3.6</v>
       </c>
       <c r="F88" s="2">
-        <v>46054</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Março</t>
-        </is>
-      </c>
-      <c r="D89">
-        <v>675.28</v>
+          <t>Dezembro</t>
+        </is>
       </c>
       <c r="F89" s="2">
-        <v>46082</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Abril</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D90">
-        <v>717.09</v>
-      </c>
-      <c r="E90">
-        <v>6.19</v>
-      </c>
-      <c r="F90" s="2">
-        <v>46113</v>
+        <v>616.47</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2502,23 +2493,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Maio</t>
-        </is>
-      </c>
-      <c r="D91">
-        <v>762.14</v>
-      </c>
-      <c r="E91">
-        <v>6.28</v>
+          <t>Janeiro</t>
+        </is>
       </c>
       <c r="F91" s="2">
-        <v>46143</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2528,17 +2513,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="F92" s="2">
-        <v>46174</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2548,17 +2533,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="F93" s="2">
-        <v>46023</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2568,17 +2553,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="F94" s="2">
-        <v>46054</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2588,17 +2573,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="F95" s="2">
-        <v>46082</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2608,20 +2593,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Abril</t>
-        </is>
-      </c>
-      <c r="D96">
-        <v>702.88</v>
+          <t>Junho</t>
+        </is>
       </c>
       <c r="F96" s="2">
-        <v>46113</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2631,17 +2613,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="F97" s="2">
-        <v>46143</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2651,17 +2633,20 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Junho</t>
-        </is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D98">
+        <v>693.98</v>
       </c>
       <c r="F98" s="2">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2681,7 +2666,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2701,7 +2686,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2715,7 +2700,7 @@
         </is>
       </c>
       <c r="D101">
-        <v>695.09</v>
+        <v>675.28</v>
       </c>
       <c r="F101" s="2">
         <v>46082</v>
@@ -2724,7 +2709,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2738,10 +2723,10 @@
         </is>
       </c>
       <c r="D102">
-        <v>726.99</v>
+        <v>717.09</v>
       </c>
       <c r="E102">
-        <v>4.59</v>
+        <v>6.19</v>
       </c>
       <c r="F102" s="2">
         <v>46113</v>
@@ -2750,7 +2735,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2762,6 +2747,12 @@
         <is>
           <t>Maio</t>
         </is>
+      </c>
+      <c r="D103">
+        <v>762.14</v>
+      </c>
+      <c r="E103">
+        <v>6.28</v>
       </c>
       <c r="F103" s="2">
         <v>46143</v>
@@ -2770,7 +2761,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2790,7 +2781,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2800,17 +2791,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="F105" s="2">
-        <v>46023</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2820,17 +2811,17 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="F106" s="2">
-        <v>46054</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2840,17 +2831,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="F107" s="2">
-        <v>46082</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2860,20 +2851,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Abril</t>
-        </is>
-      </c>
-      <c r="D108">
-        <v>593.53</v>
+          <t>Fevereiro</t>
+        </is>
       </c>
       <c r="F108" s="2">
-        <v>46113</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2883,17 +2871,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="F109" s="2">
-        <v>46143</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2903,17 +2891,20 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Junho</t>
-        </is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D110">
+        <v>702.88</v>
       </c>
       <c r="F110" s="2">
-        <v>46174</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2923,17 +2914,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="F111" s="2">
-        <v>46023</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2943,17 +2934,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="F112" s="2">
-        <v>46054</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2963,17 +2954,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="F113" s="2">
-        <v>46082</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2983,20 +2974,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Abril</t>
-        </is>
-      </c>
-      <c r="D114">
-        <v>684.72</v>
+          <t>Agosto</t>
+        </is>
       </c>
       <c r="F114" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3006,17 +2994,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Janeiro</t>
         </is>
       </c>
       <c r="F115" s="2">
-        <v>46143</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3026,17 +3014,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Fevereiro</t>
         </is>
       </c>
       <c r="F116" s="2">
-        <v>46174</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3046,17 +3034,20 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Janeiro</t>
-        </is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="D117">
+        <v>695.09</v>
       </c>
       <c r="F117" s="2">
-        <v>46023</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3066,17 +3057,23 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Fevereiro</t>
-        </is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D118">
+        <v>726.99</v>
+      </c>
+      <c r="E118">
+        <v>4.59</v>
       </c>
       <c r="F118" s="2">
-        <v>46054</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3086,17 +3083,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="F119" s="2">
-        <v>46082</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3106,20 +3103,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Abril</t>
-        </is>
-      </c>
-      <c r="D120">
-        <v>760.12</v>
+          <t>Junho</t>
+        </is>
       </c>
       <c r="F120" s="2">
-        <v>46113</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3129,31 +3123,520 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="F121" s="2">
-        <v>46143</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
+          <t>Jaraguá do Sul</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="F122" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Massaranduba</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="F123" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Massaranduba</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="F124" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Massaranduba</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="F125" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Massaranduba</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D126">
+        <v>593.53</v>
+      </c>
+      <c r="F126" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Massaranduba</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="F127" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Massaranduba</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="F128" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Massaranduba</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="F129" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Massaranduba</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="F130" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Navegantes</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="F131" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Navegantes</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="F132" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Navegantes</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="F133" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Navegantes</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D134">
+        <v>684.72</v>
+      </c>
+      <c r="F134" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Navegantes</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="F135" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Navegantes</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="F136" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Navegantes</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="F137" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Navegantes</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="F138" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
           <t>Timbó</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="F139" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="F140" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="F141" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="D142">
+        <v>760.12</v>
+      </c>
+      <c r="F142" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="F143" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
         <is>
           <t>Junho</t>
         </is>
       </c>
-      <c r="F122" s="2">
+      <c r="F144" s="2">
         <v>46174</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="F145" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="F146" s="2">
+        <v>46235</v>
       </c>
     </row>
   </sheetData>
